--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.16443174534942</v>
+        <v>3.601720158619281</v>
       </c>
       <c r="D2" t="n">
-        <v>22.25109300818895</v>
+        <v>3.615802613830705</v>
       </c>
       <c r="E2" t="n">
-        <v>21.18723326799956</v>
+        <v>3.442925406049929</v>
       </c>
       <c r="F2" t="n">
-        <v>12.86842786036272</v>
+        <v>2.091119527308943</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.12329035478989</v>
+        <v>3.270034682653358</v>
       </c>
       <c r="D3" t="n">
-        <v>20.18571421155791</v>
+        <v>3.280178559378161</v>
       </c>
       <c r="E3" t="n">
-        <v>21.18723326799956</v>
+        <v>3.442925406049929</v>
       </c>
       <c r="F3" t="n">
-        <v>12.86842786036272</v>
+        <v>2.091119527308943</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>82.57906606127567</v>
+        <v>13.4190982349573</v>
       </c>
       <c r="D4" t="n">
-        <v>33.13225444296884</v>
+        <v>5.383991346982437</v>
       </c>
       <c r="E4" t="n">
-        <v>21.18723326799956</v>
+        <v>3.442925406049929</v>
       </c>
       <c r="F4" t="n">
-        <v>12.86842786036272</v>
+        <v>2.091119527308943</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.7227346115764</v>
+        <v>9.217444374381165</v>
       </c>
       <c r="D5" t="n">
-        <v>56.78928704041578</v>
+        <v>9.228259144067565</v>
       </c>
       <c r="E5" t="n">
-        <v>21.18723326799956</v>
+        <v>3.442925406049929</v>
       </c>
       <c r="F5" t="n">
-        <v>12.86842786036272</v>
+        <v>2.091119527308943</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.41163786000354</v>
+        <v>7.054391152250576</v>
       </c>
       <c r="D6" t="n">
-        <v>43.31253890066276</v>
+        <v>7.038287571357698</v>
       </c>
       <c r="E6" t="n">
-        <v>21.18723326799956</v>
+        <v>3.442925406049929</v>
       </c>
       <c r="F6" t="n">
-        <v>12.86842786036272</v>
+        <v>2.091119527308943</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.93384334120971</v>
+        <v>7.139249542946578</v>
       </c>
       <c r="D7" t="n">
-        <v>43.91901440313183</v>
+        <v>7.136839840508922</v>
       </c>
       <c r="E7" t="n">
-        <v>21.18723326799956</v>
+        <v>3.442925406049929</v>
       </c>
       <c r="F7" t="n">
-        <v>12.86842786036272</v>
+        <v>2.091119527308943</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
